--- a/GERAL/sugestao_nomes_campos.xlsx
+++ b/GERAL/sugestao_nomes_campos.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="17235" windowHeight="9030"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="17235" windowHeight="9030" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
-    <sheet name="Plan2" sheetId="2" r:id="rId2"/>
+    <sheet name="PESSOAL" sheetId="1" r:id="rId1"/>
+    <sheet name="FUNCIONAL" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="315">
   <si>
     <t>BAIRRO</t>
   </si>
@@ -84,12 +84,6 @@
     <t>UnidPag</t>
   </si>
   <si>
-    <t>Siape</t>
-  </si>
-  <si>
-    <t>IncUfmg</t>
-  </si>
-  <si>
     <t>MesFita</t>
   </si>
   <si>
@@ -102,12 +96,6 @@
     <t>Nome</t>
   </si>
   <si>
-    <t>Cpf</t>
-  </si>
-  <si>
-    <t>Pasep</t>
-  </si>
-  <si>
     <t>Mae</t>
   </si>
   <si>
@@ -123,9 +111,6 @@
     <t>CodEstadoCiv</t>
   </si>
   <si>
-    <t>CodEscol</t>
-  </si>
-  <si>
     <t>InscUfmg</t>
   </si>
   <si>
@@ -195,9 +180,6 @@
     <t>Naturalidade</t>
   </si>
   <si>
-    <t>Codpais</t>
-  </si>
-  <si>
     <t>Pais</t>
   </si>
   <si>
@@ -207,12 +189,6 @@
     <t>Sf</t>
   </si>
   <si>
-    <t>Data1Emprego</t>
-  </si>
-  <si>
-    <t>IdOrig</t>
-  </si>
-  <si>
     <t>Logradouro</t>
   </si>
   <si>
@@ -228,9 +204,6 @@
     <t>Municipio</t>
   </si>
   <si>
-    <t>Cep</t>
-  </si>
-  <si>
     <t>Uf</t>
   </si>
   <si>
@@ -253,13 +226,748 @@
   </si>
   <si>
     <t>DepImpRenda</t>
+  </si>
+  <si>
+    <t>SIAPE</t>
+  </si>
+  <si>
+    <t>CodEscolaridade</t>
+  </si>
+  <si>
+    <t>DenoEscolaridade</t>
+  </si>
+  <si>
+    <t>CodPais</t>
+  </si>
+  <si>
+    <t>DataPrimEmprego</t>
+  </si>
+  <si>
+    <t>SIAPECAD</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>SIT</t>
+  </si>
+  <si>
+    <t>DenoSit</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>RTRAB</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>ANUE</t>
+  </si>
+  <si>
+    <t>NUMAPOS</t>
+  </si>
+  <si>
+    <t>DENAPOS</t>
+  </si>
+  <si>
+    <t>GRCARGO</t>
+  </si>
+  <si>
+    <t>CARGO</t>
+  </si>
+  <si>
+    <t>CodCargo</t>
+  </si>
+  <si>
+    <t>DenoCarg</t>
+  </si>
+  <si>
+    <t>CLAS</t>
+  </si>
+  <si>
+    <t>DenoClasse</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>SETOR</t>
+  </si>
+  <si>
+    <t>NrUorgLotacao</t>
+  </si>
+  <si>
+    <t>UnidLotacao</t>
+  </si>
+  <si>
+    <t>DenoSetorLotacao</t>
+  </si>
+  <si>
+    <t>NrUorgExercicio</t>
+  </si>
+  <si>
+    <t>UnidExercicio</t>
+  </si>
+  <si>
+    <t>DenoSetorExercicio</t>
+  </si>
+  <si>
+    <t>MunicipioUORGExercicio</t>
+  </si>
+  <si>
+    <t>EmailUORGExercicio</t>
+  </si>
+  <si>
+    <t>UorgPaiExercicio</t>
+  </si>
+  <si>
+    <t>NomeUorgPaiExercicio</t>
+  </si>
+  <si>
+    <t>NrUorgLocalAP</t>
+  </si>
+  <si>
+    <t>DenoSetorLocalAP</t>
+  </si>
+  <si>
+    <t>GREXC</t>
+  </si>
+  <si>
+    <t>DtIngOrg</t>
+  </si>
+  <si>
+    <t>DtIngSP</t>
+  </si>
+  <si>
+    <t>DtEx</t>
+  </si>
+  <si>
+    <t>DtAp</t>
+  </si>
+  <si>
+    <t>DtOb</t>
+  </si>
+  <si>
+    <t>Fun</t>
+  </si>
+  <si>
+    <t>FUNNIV</t>
+  </si>
+  <si>
+    <t>DtChefInic</t>
+  </si>
+  <si>
+    <t>DtChefFim</t>
+  </si>
+  <si>
+    <t>TemFuncao</t>
+  </si>
+  <si>
+    <t>FUNCSETOR</t>
+  </si>
+  <si>
+    <t>UnidFunc</t>
+  </si>
+  <si>
+    <t>DenoSetorFunc</t>
+  </si>
+  <si>
+    <t>FUNCESC</t>
+  </si>
+  <si>
+    <t>FUNCOPCAO</t>
+  </si>
+  <si>
+    <t>NOVFUNESCO</t>
+  </si>
+  <si>
+    <t>NOVFUNOPCA</t>
+  </si>
+  <si>
+    <t>ATIVFUNC</t>
+  </si>
+  <si>
+    <t>DENOATIV</t>
+  </si>
+  <si>
+    <t>GROCORAPOS</t>
+  </si>
+  <si>
+    <t>OCORAPOS</t>
+  </si>
+  <si>
+    <t>DenoAposent</t>
+  </si>
+  <si>
+    <t>GROCINGORG</t>
+  </si>
+  <si>
+    <t>OCINGORG</t>
+  </si>
+  <si>
+    <t>DenoIngOrgao</t>
+  </si>
+  <si>
+    <t>GROCINGSP</t>
+  </si>
+  <si>
+    <t>OCINGRSP</t>
+  </si>
+  <si>
+    <t>DenoIngServPublico</t>
+  </si>
+  <si>
+    <t>OCOREXC</t>
+  </si>
+  <si>
+    <t>DenoExclusao</t>
+  </si>
+  <si>
+    <t>SUSPPAG</t>
+  </si>
+  <si>
+    <t>DTSUSP</t>
+  </si>
+  <si>
+    <t>DTLOTAC</t>
+  </si>
+  <si>
+    <t>DTCADASTRO</t>
+  </si>
+  <si>
+    <t>DT_OCUP</t>
+  </si>
+  <si>
+    <t>DT_SAIDA</t>
+  </si>
+  <si>
+    <t>APONUMPROC</t>
+  </si>
+  <si>
+    <t>APOANOPREV</t>
+  </si>
+  <si>
+    <t>CTNUM</t>
+  </si>
+  <si>
+    <t>CT_SER</t>
+  </si>
+  <si>
+    <t>CT_UF</t>
+  </si>
+  <si>
+    <t>BANCO</t>
+  </si>
+  <si>
+    <t>AGENC</t>
+  </si>
+  <si>
+    <t>CONTA</t>
+  </si>
+  <si>
+    <t>AP_OP_INTG</t>
+  </si>
+  <si>
+    <t>APOSUORG</t>
+  </si>
+  <si>
+    <t>ORGDEST</t>
+  </si>
+  <si>
+    <t>DTLIBER</t>
+  </si>
+  <si>
+    <t>ORGORIGEM</t>
+  </si>
+  <si>
+    <t>DenoOrgOrigem</t>
+  </si>
+  <si>
+    <t>ORGANT</t>
+  </si>
+  <si>
+    <t>DenoOrgAnt</t>
+  </si>
+  <si>
+    <t>MATRICANT</t>
+  </si>
+  <si>
+    <t>ORGEXTMOD</t>
+  </si>
+  <si>
+    <t>MATSERVEXT</t>
+  </si>
+  <si>
+    <t>ORGATUAL</t>
+  </si>
+  <si>
+    <t>MATR_ATUAL</t>
+  </si>
+  <si>
+    <t>MUDUPAGCOD</t>
+  </si>
+  <si>
+    <t>MUDUPGDTLB</t>
+  </si>
+  <si>
+    <t>MUDUPGMOTI</t>
+  </si>
+  <si>
+    <t>I_PAGSERV</t>
+  </si>
+  <si>
+    <t>OBITOCART</t>
+  </si>
+  <si>
+    <t>OBITOLIVRO</t>
+  </si>
+  <si>
+    <t>OBITOFOLHA</t>
+  </si>
+  <si>
+    <t>OBITOREG</t>
+  </si>
+  <si>
+    <t>I_EXCINSTI</t>
+  </si>
+  <si>
+    <t>DTEXCINSTI</t>
+  </si>
+  <si>
+    <t>VALIMTIPO</t>
+  </si>
+  <si>
+    <t>VALIMDTINI</t>
+  </si>
+  <si>
+    <t>VALIMDTFIM</t>
+  </si>
+  <si>
+    <t>RX</t>
+  </si>
+  <si>
+    <t>ORGREQ</t>
+  </si>
+  <si>
+    <t>DenoOrgRequisitante</t>
+  </si>
+  <si>
+    <t>CODVAGA</t>
+  </si>
+  <si>
+    <t>ANUEMES</t>
+  </si>
+  <si>
+    <t>RXPERC</t>
+  </si>
+  <si>
+    <t>GOCORREVAT</t>
+  </si>
+  <si>
+    <t>OCREVERATI</t>
+  </si>
+  <si>
+    <t>DTREVERS</t>
+  </si>
+  <si>
+    <t>I_CARG</t>
+  </si>
+  <si>
+    <t>I_FUNC</t>
+  </si>
+  <si>
+    <t>I_SALFAM</t>
+  </si>
+  <si>
+    <t>I_ANUENUIO</t>
+  </si>
+  <si>
+    <t>I_FGTS</t>
+  </si>
+  <si>
+    <t>I_PSS</t>
+  </si>
+  <si>
+    <t>I_IR</t>
+  </si>
+  <si>
+    <t>I_MARGCONS</t>
+  </si>
+  <si>
+    <t>I_SINDICAL</t>
+  </si>
+  <si>
+    <t>I_ADIANT13</t>
+  </si>
+  <si>
+    <t>I_ABATETET</t>
+  </si>
+  <si>
+    <t>I_13SAL</t>
+  </si>
+  <si>
+    <t>I_PSS_6</t>
+  </si>
+  <si>
+    <t>I_FERIAS</t>
+  </si>
+  <si>
+    <t>I_PENSAO</t>
+  </si>
+  <si>
+    <t>I_BENEFICI</t>
+  </si>
+  <si>
+    <t>I_IPMF_CPM</t>
+  </si>
+  <si>
+    <t>I_RAIS</t>
+  </si>
+  <si>
+    <t>I_DIF_URV</t>
+  </si>
+  <si>
+    <t>I_ADIANTAM</t>
+  </si>
+  <si>
+    <t>I_PASEP</t>
+  </si>
+  <si>
+    <t>CodSituacao</t>
+  </si>
+  <si>
+    <t>Situacao</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>RegJuridico</t>
+  </si>
+  <si>
+    <t>CodRegTrab</t>
+  </si>
+  <si>
+    <t>RegTrabalho</t>
+  </si>
+  <si>
+    <t>NumApos</t>
+  </si>
+  <si>
+    <t>DenoApos</t>
+  </si>
+  <si>
+    <t>GrCargo</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>DenoCargo</t>
+  </si>
+  <si>
+    <t>Classe</t>
+  </si>
+  <si>
+    <t>Referencia</t>
+  </si>
+  <si>
+    <t>Setor</t>
+  </si>
+  <si>
+    <t>MunicipUorgExercicio</t>
+  </si>
+  <si>
+    <t>EmailUorgExercicio</t>
+  </si>
+  <si>
+    <t>GrExclusao</t>
+  </si>
+  <si>
+    <t>DataIngOrg</t>
+  </si>
+  <si>
+    <t>DataIngSP</t>
+  </si>
+  <si>
+    <t>DataExclusao</t>
+  </si>
+  <si>
+    <t>DataAposentadoria</t>
+  </si>
+  <si>
+    <t>DataObito</t>
+  </si>
+  <si>
+    <t>Funcao</t>
+  </si>
+  <si>
+    <t>FuncaoNivel</t>
+  </si>
+  <si>
+    <t>FuncaoSetor</t>
+  </si>
+  <si>
+    <t>UnidFuncao</t>
+  </si>
+  <si>
+    <t>FuncaoOpcao</t>
+  </si>
+  <si>
+    <t>FuncaoEscol</t>
+  </si>
+  <si>
+    <t>essa campo não tem registros escol (escolaridade, escolha)?</t>
+  </si>
+  <si>
+    <t>NovaFuncEscol</t>
+  </si>
+  <si>
+    <t>NovaFuncOpcao</t>
+  </si>
+  <si>
+    <t>CodFuncao</t>
+  </si>
+  <si>
+    <t>DenoAtividade</t>
+  </si>
+  <si>
+    <t>GrOcorrAposent</t>
+  </si>
+  <si>
+    <t>OcorrAposent</t>
+  </si>
+  <si>
+    <t>GrOcorrIngOrg</t>
+  </si>
+  <si>
+    <t>OcorrIngOrg</t>
+  </si>
+  <si>
+    <t>GrOcorrIngSp</t>
+  </si>
+  <si>
+    <t>OcorrIngSp</t>
+  </si>
+  <si>
+    <t>OcorrExclusao</t>
+  </si>
+  <si>
+    <t>SuspPagamento</t>
+  </si>
+  <si>
+    <t>DataSuspecao</t>
+  </si>
+  <si>
+    <t>DataLotacao</t>
+  </si>
+  <si>
+    <t>DataCadastro</t>
+  </si>
+  <si>
+    <t>DataOcupacao</t>
+  </si>
+  <si>
+    <t>DataSaida</t>
+  </si>
+  <si>
+    <t>AposentNumProcesso</t>
+  </si>
+  <si>
+    <t>AposentAnoPrev</t>
+  </si>
+  <si>
+    <t>CarteiraTrabNum</t>
+  </si>
+  <si>
+    <t>CarteiraTrabSerie</t>
+  </si>
+  <si>
+    <t>CarteiraTrabUf</t>
+  </si>
+  <si>
+    <t>Banco</t>
+  </si>
+  <si>
+    <t>Agencia</t>
+  </si>
+  <si>
+    <t>Conta</t>
+  </si>
+  <si>
+    <t>AposentOp_Integ</t>
+  </si>
+  <si>
+    <t>AposUorg</t>
+  </si>
+  <si>
+    <t>OrgaoDestino</t>
+  </si>
+  <si>
+    <t>DataLiberacao</t>
+  </si>
+  <si>
+    <t>OrgaoOrigem</t>
+  </si>
+  <si>
+    <t>DenoOrgaoOrigem</t>
+  </si>
+  <si>
+    <t>OrgaoAnterior</t>
+  </si>
+  <si>
+    <t>DenoOrgaoAnterior</t>
+  </si>
+  <si>
+    <t>MatricAnterior</t>
+  </si>
+  <si>
+    <t>MatServExt</t>
+  </si>
+  <si>
+    <t>OrgaoExtMod</t>
+  </si>
+  <si>
+    <t>OrgaoAtual</t>
+  </si>
+  <si>
+    <t>MatricAtual</t>
+  </si>
+  <si>
+    <t>MudancaUpagCod</t>
+  </si>
+  <si>
+    <t>MudancaUpagDataLiber</t>
+  </si>
+  <si>
+    <t>MudancaUpagMotivo</t>
+  </si>
+  <si>
+    <t>IndicePagaServ</t>
+  </si>
+  <si>
+    <t>ObitoCartorio</t>
+  </si>
+  <si>
+    <t>ObitoLivro</t>
+  </si>
+  <si>
+    <t>ObitoFolha</t>
+  </si>
+  <si>
+    <t>ObitoRegistro</t>
+  </si>
+  <si>
+    <t>IndiceExclInstituidor</t>
+  </si>
+  <si>
+    <t>DataExclInstituidor</t>
+  </si>
+  <si>
+    <t>ValeAlimTipo</t>
+  </si>
+  <si>
+    <t>ValeAlimDataInic</t>
+  </si>
+  <si>
+    <t>ValeAlimDataFim</t>
+  </si>
+  <si>
+    <t>OrgaoRequisitante</t>
+  </si>
+  <si>
+    <t>DenoOrgaoRequisitante</t>
+  </si>
+  <si>
+    <t>CodVaga</t>
+  </si>
+  <si>
+    <t>não entendi o que significa!</t>
+  </si>
+  <si>
+    <t>RxPerc</t>
+  </si>
+  <si>
+    <t>GrOcorrValeTransp</t>
+  </si>
+  <si>
+    <t>OcorenciaReversaoAtiv</t>
+  </si>
+  <si>
+    <t>DataReversao</t>
+  </si>
+  <si>
+    <t>IndiceCargo</t>
+  </si>
+  <si>
+    <t>IndiceFuncao</t>
+  </si>
+  <si>
+    <t>IndiceSalarioFamilia</t>
+  </si>
+  <si>
+    <t>IndiceAnuenio</t>
+  </si>
+  <si>
+    <t>IndiceFGTS</t>
+  </si>
+  <si>
+    <t>IndicePSS</t>
+  </si>
+  <si>
+    <t>IndiceIR</t>
+  </si>
+  <si>
+    <t>IndiceMargemConsig</t>
+  </si>
+  <si>
+    <t>indideSindical</t>
+  </si>
+  <si>
+    <t>IndiceAdiantamento13</t>
+  </si>
+  <si>
+    <t>IndiceAbateTeto</t>
+  </si>
+  <si>
+    <t>Indice13Salario</t>
+  </si>
+  <si>
+    <t>IndicePensao</t>
+  </si>
+  <si>
+    <t>IndicePSS6</t>
+  </si>
+  <si>
+    <t>IndiceFerias</t>
+  </si>
+  <si>
+    <t>IndiceBeneficio</t>
+  </si>
+  <si>
+    <t>IndiceIpmfCpm</t>
+  </si>
+  <si>
+    <t>IndiceRais</t>
+  </si>
+  <si>
+    <t>IndiceDifURV</t>
+  </si>
+  <si>
+    <t>IndiceAdiantamento</t>
+  </si>
+  <si>
+    <t>IndicePasep</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,6 +981,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -336,16 +1050,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,17 +1373,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -678,10 +1396,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -689,7 +1407,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -697,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -705,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -713,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -721,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -729,7 +1447,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -737,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -745,23 +1463,23 @@
         <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -769,15 +1487,15 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -785,55 +1503,55 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -841,55 +1559,55 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -897,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -905,7 +1623,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -913,7 +1631,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -921,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -929,7 +1647,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -937,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -945,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -953,39 +1671,39 @@
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -999,10 +1717,1102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:C135"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/GERAL/sugestao_nomes_campos.xlsx
+++ b/GERAL/sugestao_nomes_campos.xlsx
@@ -798,9 +798,6 @@
     <t>Conta</t>
   </si>
   <si>
-    <t>AposentOp_Integ</t>
-  </si>
-  <si>
     <t>AposUorg</t>
   </si>
   <si>
@@ -961,13 +958,16 @@
   </si>
   <si>
     <t>IndicePasep</t>
+  </si>
+  <si>
+    <t>AposentOpInteg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -988,13 +988,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -1050,20 +1063,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1373,10 +1387,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1720,399 +1734,399 @@
   <dimension ref="A1:C135"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>233</v>
       </c>
       <c r="C49" t="s">
@@ -2120,699 +2134,700 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="4" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="4" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C80" s="7"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B81" s="6" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" s="6" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B83" s="6" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" s="6" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B85" s="6" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="6" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B87" s="6" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B88" s="6" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B89" s="6" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B91" s="6" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B92" s="6" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B93" s="6" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B94" s="6" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B95" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B95" s="6" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B96" s="6" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B97" s="6" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B98" s="6" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B99" s="6" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B100" s="6" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B101" s="6" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B102" s="6" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B103" s="6" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B104" s="6" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B105" s="6" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B107" s="6" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B108" s="6" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B109" s="6" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C110" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B111" s="6" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B112" s="6" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B113" s="6" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B114" s="6" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B115" s="6" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B116" s="6" t="s">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B117" s="6" t="s">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B118" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B118" s="6" t="s">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B119" s="6" t="s">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B120" s="6" t="s">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B121" s="6" t="s">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B122" s="6" t="s">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B123" s="6" t="s">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B124" s="6" t="s">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B125" s="6" t="s">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B126" s="6" t="s">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B128" s="6" t="s">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B130" s="6" t="s">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B131" s="6" t="s">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B132" s="6" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B133" s="6" t="s">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B134" s="6" t="s">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>314</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
